--- a/Entrega 3/Soza_Vicente_vis_01/Base de Datos Elecciones y Candidatos Excel.xlsx
+++ b/Entrega 3/Soza_Vicente_vis_01/Base de Datos Elecciones y Candidatos Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d68ecb513cfe30c0/Escritorio/Entrega-1/Entrega 3/Soza_Vicente_vis_01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CF33E1B-EA05-486E-88ED-FCC917EF8813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{6CF33E1B-EA05-486E-88ED-FCC917EF8813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6C3A355-1592-4BD0-B57F-009E5B247CAF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A3797EEA-1AEB-4F58-87B8-1F76CF22964F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="68">
   <si>
     <t>Candidatos</t>
   </si>
@@ -149,12 +149,6 @@
   </si>
   <si>
     <t>ME-O</t>
-  </si>
-  <si>
-    <t>Piñera</t>
-  </si>
-  <si>
-    <t>Frei</t>
   </si>
   <si>
     <t>2009.1</t>
@@ -2680,7 +2674,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>2009</v>
@@ -2739,7 +2733,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>2009</v>
@@ -2801,7 +2795,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29">
         <v>56710</v>
@@ -2866,7 +2860,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>36823</v>
@@ -2922,7 +2916,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B31">
         <v>2013</v>
@@ -2978,7 +2972,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B32">
         <v>2013</v>
@@ -3034,7 +3028,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33">
         <v>2013</v>
@@ -3146,7 +3140,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B35">
         <v>2013</v>
@@ -3258,7 +3252,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>2013</v>
@@ -3314,7 +3308,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B38">
         <v>2013</v>
@@ -3370,7 +3364,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B39">
         <v>2013</v>
@@ -3426,10 +3420,10 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>27626</v>
@@ -3494,7 +3488,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C41">
         <v>36343</v>
@@ -3550,7 +3544,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B42">
         <v>2017</v>
@@ -3609,7 +3603,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>2017</v>
@@ -3727,7 +3721,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B45">
         <v>2017</v>
@@ -3786,7 +3780,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B46">
         <v>2017</v>
@@ -3910,7 +3904,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>2017</v>
@@ -3969,7 +3963,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49">
         <v>2017</v>
@@ -4031,7 +4025,7 @@
         <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C50">
         <v>54379</v>
@@ -4093,10 +4087,10 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C51">
         <v>38106</v>
@@ -4152,7 +4146,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B52">
         <v>2021</v>
@@ -4217,7 +4211,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B53">
         <v>2021</v>
@@ -4276,7 +4270,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B54">
         <v>2021</v>
@@ -4335,7 +4329,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B55">
         <v>2021</v>
@@ -4394,7 +4388,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B56">
         <v>2021</v>
@@ -4512,7 +4506,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B58">
         <v>2021</v>
@@ -4571,10 +4565,10 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C59">
         <v>55477</v>
@@ -4636,10 +4630,10 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60">
         <v>58485</v>
@@ -4695,7 +4689,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B61">
         <v>2025</v>
@@ -4760,7 +4754,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B62">
         <v>2025</v>
@@ -4878,7 +4872,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B64">
         <v>2025</v>
@@ -4937,7 +4931,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B65">
         <v>2025</v>
@@ -4996,7 +4990,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B66">
         <v>2025</v>
@@ -5055,7 +5049,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B67">
         <v>2025</v>
@@ -5114,7 +5108,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B68">
         <v>2025</v>
@@ -5173,10 +5167,10 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C69">
         <v>73799</v>
@@ -5238,10 +5232,10 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C70">
         <v>120980</v>
